--- a/Таблицы Данных/Conducting an experiment 30_08.xlsx
+++ b/Таблицы Данных/Conducting an experiment 30_08.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10517"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bogda/Desktop/Acoustics/Scientific/Таблицы Данных/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBE1177-BCC1-BC43-B797-CEB19B97E634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DF3898-1517-694A-9F8F-98D61BBC88A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Measurement" sheetId="3" r:id="rId1"/>
@@ -326,7 +326,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,6 +359,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -401,7 +407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -411,10 +417,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -435,15 +441,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -453,15 +450,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -471,13 +465,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -486,9 +477,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -496,6 +484,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -987,11 +978,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.1640625" style="1"/>
-    <col min="2" max="2" width="10.83203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="21" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.1640625" style="1" customWidth="1"/>
@@ -1005,7 +996,7 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -1028,10 +1019,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="21">
         <v>0.61678240740740697</v>
       </c>
       <c r="C2" s="7">
@@ -1054,10 +1045,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="21">
         <v>0.61782407407407403</v>
       </c>
       <c r="C3" s="7">
@@ -1080,10 +1071,10 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="22">
         <v>0.61972222222222195</v>
       </c>
       <c r="C4" s="9">
@@ -1106,10 +1097,10 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="21">
         <v>0.62008101851851805</v>
       </c>
       <c r="C5" s="7">
@@ -1129,10 +1120,10 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="21">
         <v>0.620960648148148</v>
       </c>
       <c r="C6" s="7">
@@ -1151,13 +1142,13 @@
       <c r="H6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="20"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="21">
         <v>0.62189814814814803</v>
       </c>
       <c r="C7" s="7">
@@ -1180,25 +1171,25 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="21">
         <v>0.62256944444444395</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="7">
         <v>3.4722222222222202E-4</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="2">
         <v>100</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="2">
         <v>200</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -1206,10 +1197,10 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="21">
         <v>0.623113425925926</v>
       </c>
       <c r="C9" s="7">
@@ -1232,10 +1223,10 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="21">
         <v>0.62356481481481496</v>
       </c>
       <c r="C10" s="7">
@@ -1261,10 +1252,10 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="21">
         <v>0.62443287037036999</v>
       </c>
       <c r="C11" s="7">
@@ -1287,10 +1278,10 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="21">
         <v>0.62612268518518499</v>
       </c>
       <c r="C12" s="7">
@@ -1313,10 +1304,10 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="21">
         <v>0.626886574074074</v>
       </c>
       <c r="C13" s="7">
@@ -1339,10 +1330,10 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="21">
         <v>0.62929398148148197</v>
       </c>
       <c r="C14" s="7">
@@ -1365,10 +1356,10 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="21">
         <v>0.62975694444444397</v>
       </c>
       <c r="C15" s="7">
@@ -1391,10 +1382,10 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="21">
         <v>0.63032407407407398</v>
       </c>
       <c r="C16" s="7">
@@ -1416,11 +1407,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="21" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="21">
         <v>0.63076388888888901</v>
       </c>
       <c r="C17" s="7">
@@ -1442,11 +1433,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="21" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="21">
         <v>0.63131944444444399</v>
       </c>
       <c r="C18" s="7">
@@ -1468,86 +1459,85 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="23">
         <v>0.63348379629629603</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="12">
         <v>4.5138888888888898E-4</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="14" t="s">
+      <c r="D19" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="17" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="21">
         <v>0.63725694444444403</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="7">
         <v>4.7453703703703698E-4</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="11" t="s">
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="23" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="21">
         <v>0.63929398148148198</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="7">
         <v>1.1226851851851901E-3</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="11" t="s">
+      <c r="E21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I21" s="11"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="21">
         <v>0.64047453703703705</v>
       </c>
       <c r="C22" s="7">
@@ -1566,13 +1556,12 @@
       <c r="H22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I22" s="11"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="21" t="s">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="21">
         <v>0.64423611111111101</v>
       </c>
       <c r="C23" s="7">
@@ -1592,11 +1581,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="21">
         <v>0.64526620370370402</v>
       </c>
       <c r="C24" s="7">
@@ -1613,11 +1602,11 @@
       </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="21" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="21">
         <v>0.64603009259259303</v>
       </c>
       <c r="C25" s="7">
@@ -1634,11 +1623,11 @@
       </c>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="21" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="21">
         <v>0.64645833333333302</v>
       </c>
       <c r="C26" s="7">
@@ -1660,11 +1649,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="21" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="21">
         <v>0.647280092592593</v>
       </c>
       <c r="C27" s="7">
@@ -1686,33 +1675,33 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="18" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="23">
         <v>0.64798611111111104</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="12">
         <v>4.6296296296296298E-4</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="13">
         <v>50</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="13">
         <v>50</v>
       </c>
-      <c r="G28" s="16"/>
-      <c r="H28" s="14"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="21" t="s">
+      <c r="G28" s="13"/>
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="21">
         <v>0.65388888888888896</v>
       </c>
       <c r="C29" s="7">
@@ -1731,11 +1720,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="21" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="21">
         <v>0.65497685185185195</v>
       </c>
       <c r="C30" s="7">
@@ -1754,11 +1743,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="21">
         <v>0.65577546296296296</v>
       </c>
       <c r="C31" s="7">
@@ -1777,11 +1766,11 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="21" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="21">
         <v>0.65668981481481503</v>
       </c>
       <c r="C32" s="7">
@@ -1804,10 +1793,10 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="21">
         <v>0.65833333333333299</v>
       </c>
       <c r="C33" s="7">
@@ -1830,34 +1819,34 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="23">
         <v>0.66221064814814801</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="12">
         <v>6.5972222222222203E-4</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="13">
         <v>2</v>
       </c>
-      <c r="F34" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14" t="s">
+      <c r="F34" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="21">
         <v>0.66824074074074102</v>
       </c>
       <c r="C35" s="7">
@@ -1877,10 +1866,10 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="21">
         <v>0.66885416666666697</v>
       </c>
       <c r="C36" s="7">
@@ -1897,10 +1886,10 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="21">
         <v>0.66988425925925899</v>
       </c>
       <c r="C37" s="7">
@@ -1917,10 +1906,10 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="21">
         <v>0.67061342592592599</v>
       </c>
       <c r="C38" s="7">
@@ -1937,10 +1926,10 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="26">
+      <c r="B39" s="21">
         <v>0.67096064814814804</v>
       </c>
       <c r="C39" s="7">
@@ -1963,10 +1952,10 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="26">
+      <c r="B40" s="21">
         <v>0.67163194444444396</v>
       </c>
       <c r="C40" s="7">
@@ -1989,10 +1978,10 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="26">
+      <c r="B41" s="21">
         <v>0.67322916666666699</v>
       </c>
       <c r="C41" s="7">
@@ -2012,10 +2001,10 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="21">
         <v>0.67519675925925904</v>
       </c>
       <c r="C42" s="7">
@@ -2031,10 +2020,10 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="19" t="s">
+      <c r="A43" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="26">
+      <c r="B43" s="21">
         <v>0.67598379629629601</v>
       </c>
       <c r="C43" s="7">
@@ -2048,34 +2037,34 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
+      <c r="A44" s="14"/>
       <c r="C44" s="7"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="30"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
+      <c r="A45" s="24"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="30">
+      <c r="A46" s="24">
         <v>44</v>
       </c>
-      <c r="B46" s="31">
+      <c r="B46" s="25">
         <v>0.64965277777777775</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="25">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="D46" s="30" t="s">
+      <c r="D46" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
       <c r="H46" s="1" t="s">
         <v>84</v>
       </c>
@@ -2084,7 +2073,7 @@
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47" s="26">
+      <c r="B47" s="21">
         <v>0.64674768518518522</v>
       </c>
       <c r="C47" s="7">
@@ -2098,7 +2087,7 @@
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48" s="26">
+      <c r="B48" s="21">
         <v>0.64725694444444437</v>
       </c>
       <c r="C48" s="7">
@@ -2112,10 +2101,10 @@
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49" s="31">
+      <c r="B49" s="25">
         <v>0.64674768518518522</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="25">
         <v>5.7870370370370378E-4</v>
       </c>
       <c r="H49" s="1" t="s">
@@ -2126,7 +2115,7 @@
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50" s="26">
+      <c r="B50" s="21">
         <v>0.67598379629629601</v>
       </c>
       <c r="C50" s="7">
@@ -2137,10 +2126,10 @@
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51" s="31">
+      <c r="B51" s="25">
         <v>0.64967592592592593</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="25">
         <v>1.1574074074074073E-5</v>
       </c>
       <c r="H51" s="1" t="s">
@@ -2151,10 +2140,10 @@
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52" s="31">
+      <c r="B52" s="25">
         <v>0.64324074074074067</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="25">
         <v>8.3333333333333332E-3</v>
       </c>
       <c r="H52" s="1" t="s">
@@ -2165,10 +2154,10 @@
       <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53" s="26">
+      <c r="B53" s="21">
         <v>0.64677083333333341</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="25">
         <v>1.1574074074074073E-5</v>
       </c>
       <c r="H53" s="1" t="s">
@@ -2179,10 +2168,10 @@
       <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B54" s="26">
+      <c r="B54" s="21">
         <v>0.67673611111111109</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="25">
         <v>1.1574074074074073E-5</v>
       </c>
     </row>
@@ -2190,7 +2179,7 @@
       <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55" s="26">
+      <c r="B55" s="21">
         <v>0.64810185185185187</v>
       </c>
       <c r="C55" s="7">
@@ -2204,7 +2193,7 @@
       <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="21">
         <v>0.65087962962962964</v>
       </c>
       <c r="C56" s="7">
@@ -2218,7 +2207,7 @@
       <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="21">
         <v>0.65226851851851853</v>
       </c>
       <c r="C57" s="7">
@@ -2229,7 +2218,7 @@
       <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B58" s="31">
+      <c r="B58" s="25">
         <v>0.64324074074074067</v>
       </c>
       <c r="C58" s="7">
@@ -2243,7 +2232,7 @@
       <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="21">
         <v>0.64682870370370371</v>
       </c>
       <c r="C59" s="7">
@@ -2257,7 +2246,7 @@
       <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="21">
         <v>0.64671296296296299</v>
       </c>
       <c r="C60" s="7">
@@ -2265,43 +2254,161 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="1">
+      <c r="A61" s="26">
         <v>59</v>
       </c>
-      <c r="B61" s="26">
-        <v>0.64687499999999998</v>
+      <c r="B61" s="21">
+        <v>0.64678240740740744</v>
       </c>
       <c r="C61" s="7">
         <v>1.1574074074074073E-5</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="1">
+      <c r="A62" s="26">
         <v>60</v>
       </c>
-      <c r="B62" s="26">
-        <v>0.64682870370370371</v>
+      <c r="B62" s="21">
+        <v>0.64679398148148148</v>
       </c>
       <c r="C62" s="7">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="1">
+      <c r="A63" s="26">
         <v>61</v>
       </c>
-      <c r="B63" s="26">
-        <v>0.64688657407407402</v>
+      <c r="B63" s="21">
+        <v>0.64680555555555552</v>
       </c>
       <c r="C63" s="7">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="H63" s="1" t="s">
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="26">
+        <v>62</v>
+      </c>
+      <c r="B64" s="21">
+        <v>0.64681712962962967</v>
+      </c>
+      <c r="C64" s="7">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="26">
+        <v>63</v>
+      </c>
+      <c r="B65" s="21">
+        <v>0.64682870370370371</v>
+      </c>
+      <c r="C65" s="7">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="26">
+        <v>64</v>
+      </c>
+      <c r="B66" s="21">
+        <v>0.64684027777777775</v>
+      </c>
+      <c r="C66" s="7">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="H66" s="26"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="26">
+        <v>65</v>
+      </c>
+      <c r="B67" s="21">
+        <v>0.6468518518518519</v>
+      </c>
+      <c r="C67" s="7">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="26">
+        <v>66</v>
+      </c>
+      <c r="B68" s="21">
+        <v>0.64686342592592594</v>
+      </c>
+      <c r="C68" s="7">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="26">
+        <v>67</v>
+      </c>
+      <c r="B69" s="21">
+        <v>0.64687499999999998</v>
+      </c>
+      <c r="C69" s="7">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" s="26">
+        <v>68</v>
+      </c>
+      <c r="B70" s="21">
+        <v>0.64688657407407402</v>
+      </c>
+      <c r="C70" s="7">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>94</v>
       </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" s="26"/>
+      <c r="C71" s="7"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" s="26"/>
+      <c r="C72" s="7"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" s="26"/>
+      <c r="C73" s="7"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="26"/>
+      <c r="C74" s="7"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="26"/>
+      <c r="C75" s="7"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="26"/>
+      <c r="C76" s="7"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="26"/>
+      <c r="C77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="26"/>
+      <c r="C78" s="7"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="26"/>
+      <c r="C79" s="7"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="26"/>
+      <c r="C80" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Таблицы Данных/Conducting an experiment 30_08.xlsx
+++ b/Таблицы Данных/Conducting an experiment 30_08.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bogda/Desktop/Acoustics/Scientific/Таблицы Данных/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DF3898-1517-694A-9F8F-98D61BBC88A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06109BB4-E61D-284A-AEBA-30F37D30C5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3620" windowWidth="29400" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Measurement" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>дистанция примерно 150 метров (расстояние 158)</t>
+  </si>
+  <si>
+    <t>пролет близко</t>
   </si>
 </sst>
 </file>
@@ -2371,8 +2374,18 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="26"/>
-      <c r="C71" s="7"/>
+      <c r="A71" s="1">
+        <v>69</v>
+      </c>
+      <c r="B71" s="25">
+        <v>0.64652777777777781</v>
+      </c>
+      <c r="C71" s="25">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="H71" s="26" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="26"/>

--- a/Таблицы Данных/Conducting an experiment 30_08.xlsx
+++ b/Таблицы Данных/Conducting an experiment 30_08.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10525"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06109BB4-E61D-284A-AEBA-30F37D30C5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3620" windowWidth="29400" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Measurement" sheetId="3" r:id="rId1"/>
